--- a/internal/pkg/batchconvert/testfiles/input/mixed/Umsaetze.xlsx
+++ b/internal/pkg/batchconvert/testfiles/input/mixed/Umsaetze.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
+  <workbookPr showObjects="all"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId3" state="visible"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
+  <calcPr iterateCount="100" iterateDelta="0.001" refMode="A1"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1ExcelA1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="90">
   <si>
     <t xml:space="preserve">Transaktionsansicht</t>
   </si>
@@ -251,49 +251,88 @@
   </si>
   <si>
     <t xml:space="preserve">Detail6</t>
+  </si>
+  <si>
+    <t>Kiosk Am Markt</t>
+  </si>
+  <si>
+    <t>KIOSK AM MARKT     BERLIN     DE</t>
+  </si>
+  <si>
+    <t>PayPal Europe</t>
+  </si>
+  <si>
+    <t>XYZ  Rotterdam</t>
+  </si>
+  <si>
+    <t>Abc</t>
+  </si>
+  <si>
+    <t>DB Fernverkehr AG</t>
+  </si>
+  <si>
+    <t>Bank Ort</t>
+  </si>
+  <si>
+    <t>DB Bahn</t>
+  </si>
+  <si>
+    <t>98765432109876543210993</t>
+  </si>
+  <si>
+    <t>08.09.2020</t>
+  </si>
+  <si>
+    <t>20,00 €</t>
+  </si>
+  <si>
+    <t>Gutschrift</t>
+  </si>
+  <si>
+    <t>Erstattung DB Bahn</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0"/>
   </numFmts>
   <fonts count="6">
     <font>
+      <name val="Calibri"/>
+      <charset val="1"/>
+      <family val="0"/>
       <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="0"/>
-      <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <sz val="10"/>
     </font>
     <font>
-      <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <sz val="10"/>
     </font>
     <font>
-      <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <sz val="10"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <charset val="1"/>
+      <family val="0"/>
       <sz val="16"/>
-      <name val="Calibri"/>
-      <family val="0"/>
-      <charset val="1"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <charset val="1"/>
+      <family val="0"/>
       <sz val="10"/>
-      <name val="Calibri"/>
-      <family val="0"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -311,14 +350,14 @@
     </fill>
   </fills>
   <borders count="2">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left style="thin"/>
       <right style="thin"/>
       <top style="thin"/>
@@ -328,8 +367,8 @@
   </borders>
   <cellStyleXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+      <alignment horizontal="general" vertical="bottom"/>
+      <protection hidden="false" locked="true"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
@@ -353,24 +392,24 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+      <alignment horizontal="general" vertical="bottom"/>
+      <protection hidden="false" locked="true"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+      <alignment horizontal="general" vertical="bottom"/>
+      <protection hidden="false" locked="true"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+      <alignment horizontal="general" vertical="bottom"/>
+      <protection hidden="false" locked="true"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="false" locked="true"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="false" locked="true"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -487,14 +526,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Arial" pitchFamily="0"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Arial" pitchFamily="0"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme>
@@ -547,40 +586,42 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+  <sheetPr>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O20"/>
-  <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="23.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="27.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="13.94"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="38.96"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="10.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="16.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="14.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="19.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="5.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="23.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="14.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="21.64"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="11.63"/>
+    <col customWidth="true" max="1" min="1" style="1" width="23.56"/>
+    <col customWidth="true" max="2" min="2" style="1" width="27.42"/>
+    <col customWidth="true" max="4" min="3" style="1" width="13.94"/>
+    <col customWidth="true" max="5" min="5" style="1" width="38.96"/>
+    <col customWidth="true" max="7" min="6" style="1" width="10.09"/>
+    <col customWidth="true" max="8" min="8" style="1" width="16.83"/>
+    <col customWidth="true" max="9" min="9" style="1" width="14.89"/>
+    <col customWidth="true" max="10" min="10" style="1" width="19.71"/>
+    <col customWidth="true" max="11" min="11" style="1" width="5.28"/>
+    <col customWidth="true" max="12" min="12" style="1" width="23.56"/>
+    <col customWidth="true" max="13" min="13" style="1" width="14.89"/>
+    <col customWidth="true" max="14" min="14" style="1" width="21.64"/>
+    <col customWidth="true" max="15" min="15" style="1" width="11.63"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" ht="13.8"/>
+    <row r="2" ht="19.7">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" ht="13.8"/>
+    <row r="4" ht="13.8">
       <c r="A4" s="3" t="s">
         <v>1</v>
       </c>
@@ -588,7 +629,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" ht="13.8">
       <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
@@ -596,7 +637,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" ht="13.8">
       <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
@@ -604,7 +645,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" ht="13.8">
       <c r="A7" s="3" t="s">
         <v>7</v>
       </c>
@@ -612,7 +653,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" ht="13.8">
       <c r="A8" s="3" t="s">
         <v>9</v>
       </c>
@@ -620,7 +661,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" ht="13.8">
       <c r="A9" s="3" t="s">
         <v>11</v>
       </c>
@@ -628,7 +669,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" ht="13.8">
       <c r="A10" s="3" t="s">
         <v>13</v>
       </c>
@@ -636,7 +677,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" ht="13.8">
       <c r="A11" s="3" t="s">
         <v>15</v>
       </c>
@@ -644,8 +685,8 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" ht="13.8"/>
+    <row r="13" ht="12.8">
       <c r="A13" s="3" t="s">
         <v>17</v>
       </c>
@@ -692,7 +733,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" ht="13.8">
       <c r="A14" s="4" t="s">
         <v>30</v>
       </c>
@@ -703,7 +744,7 @@
         <v>32</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>33</v>
+        <v>77</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>34</v>
@@ -730,10 +771,10 @@
         <v>38</v>
       </c>
       <c r="O14" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="15" ht="12.8">
       <c r="A15" s="4" t="s">
         <v>42</v>
       </c>
@@ -747,7 +788,7 @@
         <v>44</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>45</v>
+        <v>79</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>34</v>
@@ -777,10 +818,10 @@
         <v>38</v>
       </c>
       <c r="O15" s="4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="16" ht="12.8">
       <c r="A16" s="4" t="s">
         <v>49</v>
       </c>
@@ -794,7 +835,7 @@
         <v>52</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>34</v>
@@ -822,10 +863,10 @@
         <v>38</v>
       </c>
       <c r="O16" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="17" ht="12.8">
       <c r="A17" s="4" t="s">
         <v>55</v>
       </c>
@@ -839,7 +880,7 @@
         <v>58</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>34</v>
@@ -869,10 +910,10 @@
         <v>38</v>
       </c>
       <c r="O17" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="18" ht="12.8">
       <c r="A18" s="4" t="s">
         <v>61</v>
       </c>
@@ -886,7 +927,7 @@
         <v>62</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="F18" s="4" t="s">
         <v>34</v>
@@ -916,10 +957,10 @@
         <v>38</v>
       </c>
       <c r="O18" s="4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="19" ht="12.8">
       <c r="A19" s="4" t="s">
         <v>65</v>
       </c>
@@ -933,7 +974,7 @@
         <v>67</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>34</v>
@@ -963,10 +1004,10 @@
         <v>38</v>
       </c>
       <c r="O19" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="20" ht="12.8">
       <c r="A20" s="4" t="s">
         <v>71</v>
       </c>
@@ -980,7 +1021,7 @@
         <v>74</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>34</v>
@@ -1010,16 +1051,60 @@
         <v>38</v>
       </c>
       <c r="O20" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="M21" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="N21" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="O21" s="1" t="s">
+        <v>89</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <printOptions gridLinesSet="true"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup cellComments="none" copies="1" fitToHeight="1" fitToWidth="1" horizontalDpi="300" orientation="portrait" pageOrder="downThenOver" paperSize="9" scale="100" verticalDpi="300"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/internal/pkg/batchconvert/testfiles/input/mixed/Umsaetze.xlsx
+++ b/internal/pkg/batchconvert/testfiles/input/mixed/Umsaetze.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
-  <workbookPr showObjects="all"/>
+  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId3" state="visible"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr iterateCount="100" iterateDelta="0.001" refMode="A1"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1ExcelA1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="90">
   <si>
     <t xml:space="preserve">Transaktionsansicht</t>
   </si>
@@ -253,86 +253,86 @@
     <t xml:space="preserve">Detail6</t>
   </si>
   <si>
-    <t>Kiosk Am Markt</t>
-  </si>
-  <si>
-    <t>KIOSK AM MARKT     BERLIN     DE</t>
-  </si>
-  <si>
-    <t>PayPal Europe</t>
-  </si>
-  <si>
-    <t>XYZ  Rotterdam</t>
-  </si>
-  <si>
-    <t>Abc</t>
-  </si>
-  <si>
-    <t>DB Fernverkehr AG</t>
-  </si>
-  <si>
-    <t>Bank Ort</t>
-  </si>
-  <si>
-    <t>DB Bahn</t>
-  </si>
-  <si>
-    <t>98765432109876543210993</t>
-  </si>
-  <si>
-    <t>08.09.2020</t>
-  </si>
-  <si>
-    <t>20,00 €</t>
-  </si>
-  <si>
-    <t>Gutschrift</t>
-  </si>
-  <si>
-    <t>Erstattung DB Bahn</t>
+    <t xml:space="preserve">Kiosk Am Markt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIOSK AM MARKT     BERLIN     DE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PayPal Europe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XYZ  Rotterdam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DB Fernverkehr AG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bank Ort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DB Bahn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98765432109876543210993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08.09.2020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20,00 €</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gutschrift</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Erstattung DB Bahn</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0"/>
   </numFmts>
   <fonts count="6">
     <font>
+      <sz val="11"/>
       <name val="Calibri"/>
+      <family val="0"/>
       <charset val="1"/>
-      <family val="0"/>
-      <sz val="11"/>
     </font>
     <font>
+      <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-      <sz val="10"/>
     </font>
     <font>
+      <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-      <sz val="10"/>
     </font>
     <font>
+      <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-      <sz val="10"/>
     </font>
     <font>
+      <sz val="16"/>
       <name val="Calibri"/>
+      <family val="0"/>
       <charset val="1"/>
-      <family val="0"/>
-      <sz val="16"/>
     </font>
     <font>
+      <sz val="10"/>
       <name val="Calibri"/>
+      <family val="0"/>
       <charset val="1"/>
-      <family val="0"/>
-      <sz val="10"/>
     </font>
   </fonts>
   <fills count="3">
@@ -350,14 +350,14 @@
     </fill>
   </fills>
   <borders count="2">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left style="thin"/>
       <right style="thin"/>
       <top style="thin"/>
@@ -367,8 +367,8 @@
   </borders>
   <cellStyleXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom"/>
-      <protection hidden="false" locked="true"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
@@ -392,24 +392,24 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom"/>
-      <protection hidden="false" locked="true"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom"/>
-      <protection hidden="false" locked="true"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom"/>
-      <protection hidden="false" locked="true"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="false" locked="true"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="false" locked="true"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -526,14 +526,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Arial" pitchFamily="0"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0"/>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial" pitchFamily="0"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0"/>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme>
@@ -586,42 +586,40 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr>
-    <pageSetUpPr/>
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O20"/>
-  <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8"/>
+  <dimension ref="A1:O21"/>
+  <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col customWidth="true" max="1" min="1" style="1" width="23.56"/>
-    <col customWidth="true" max="2" min="2" style="1" width="27.42"/>
-    <col customWidth="true" max="4" min="3" style="1" width="13.94"/>
-    <col customWidth="true" max="5" min="5" style="1" width="38.96"/>
-    <col customWidth="true" max="7" min="6" style="1" width="10.09"/>
-    <col customWidth="true" max="8" min="8" style="1" width="16.83"/>
-    <col customWidth="true" max="9" min="9" style="1" width="14.89"/>
-    <col customWidth="true" max="10" min="10" style="1" width="19.71"/>
-    <col customWidth="true" max="11" min="11" style="1" width="5.28"/>
-    <col customWidth="true" max="12" min="12" style="1" width="23.56"/>
-    <col customWidth="true" max="13" min="13" style="1" width="14.89"/>
-    <col customWidth="true" max="14" min="14" style="1" width="21.64"/>
-    <col customWidth="true" max="15" min="15" style="1" width="11.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="23.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="27.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="13.94"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="38.96"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="10.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="16.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="14.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="19.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="5.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="23.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="14.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="21.64"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="11.63"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.8"/>
-    <row r="2" ht="19.7">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" ht="13.8"/>
-    <row r="4" ht="13.8">
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
         <v>1</v>
       </c>
@@ -629,7 +627,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" ht="13.8">
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
@@ -637,7 +635,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" ht="13.8">
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
@@ -645,7 +643,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" ht="13.8">
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
         <v>7</v>
       </c>
@@ -653,7 +651,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" ht="13.8">
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
         <v>9</v>
       </c>
@@ -661,7 +659,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" ht="13.8">
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
         <v>11</v>
       </c>
@@ -669,7 +667,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" ht="13.8">
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
         <v>13</v>
       </c>
@@ -677,7 +675,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" ht="13.8">
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
         <v>15</v>
       </c>
@@ -685,8 +683,8 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" ht="13.8"/>
-    <row r="13" ht="12.8">
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
         <v>17</v>
       </c>
@@ -733,7 +731,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="14" ht="13.8">
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
         <v>30</v>
       </c>
@@ -774,7 +772,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="15" ht="12.8">
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
         <v>42</v>
       </c>
@@ -821,7 +819,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="16" ht="12.8">
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
         <v>49</v>
       </c>
@@ -866,7 +864,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="17" ht="12.8">
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
         <v>55</v>
       </c>
@@ -913,7 +911,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="18" ht="12.8">
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
         <v>61</v>
       </c>
@@ -960,7 +958,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="19" ht="12.8">
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
         <v>65</v>
       </c>
@@ -1007,7 +1005,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="20" ht="12.8">
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
         <v>71</v>
       </c>
@@ -1054,57 +1052,60 @@
         <v>75</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="1" t="s">
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D21" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="E21" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="F21" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="G21" s="1" t="s">
+      <c r="G21" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="H21" s="1" t="s">
+      <c r="H21" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="I21" s="1" t="s">
+      <c r="I21" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="J21" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="K21" s="1" t="s">
+      <c r="J21" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="K21" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="L21" s="1" t="s">
+      <c r="L21" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="M21" s="1" t="s">
+      <c r="M21" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="N21" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="O21" s="1" t="s">
+      <c r="N21" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="O21" s="4" t="s">
         <v>89</v>
       </c>
     </row>
   </sheetData>
-  <printOptions gridLinesSet="true"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup cellComments="none" copies="1" fitToHeight="1" fitToWidth="1" horizontalDpi="300" orientation="portrait" pageOrder="downThenOver" paperSize="9" scale="100" verticalDpi="300"/>
-  <headerFooter/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/internal/pkg/batchconvert/testfiles/input/mixed/Umsaetze.xlsx
+++ b/internal/pkg/batchconvert/testfiles/input/mixed/Umsaetze.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="90">
   <si>
     <t xml:space="preserve">Transaktionsansicht</t>
   </si>
@@ -251,6 +251,45 @@
   </si>
   <si>
     <t xml:space="preserve">Detail6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kiosk Am Markt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIOSK AM MARKT     BERLIN     DE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PayPal Europe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XYZ  Rotterdam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DB Fernverkehr AG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bank Ort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DB Bahn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98765432109876543210993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08.09.2020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20,00 €</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gutschrift</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Erstattung DB Bahn</t>
   </si>
 </sst>
 </file>
@@ -555,7 +594,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O20"/>
+  <dimension ref="A1:O21"/>
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="23.56"/>
@@ -703,7 +742,7 @@
         <v>32</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>33</v>
+        <v>77</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>34</v>
@@ -730,7 +769,7 @@
         <v>38</v>
       </c>
       <c r="O14" s="4" t="s">
-        <v>41</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -747,7 +786,7 @@
         <v>44</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>45</v>
+        <v>79</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>34</v>
@@ -777,7 +816,7 @@
         <v>38</v>
       </c>
       <c r="O15" s="4" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -794,7 +833,7 @@
         <v>52</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>34</v>
@@ -822,7 +861,7 @@
         <v>38</v>
       </c>
       <c r="O16" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -839,7 +878,7 @@
         <v>58</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>34</v>
@@ -869,7 +908,7 @@
         <v>38</v>
       </c>
       <c r="O17" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -886,7 +925,7 @@
         <v>62</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="F18" s="4" t="s">
         <v>34</v>
@@ -916,7 +955,7 @@
         <v>38</v>
       </c>
       <c r="O18" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -933,7 +972,7 @@
         <v>67</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>34</v>
@@ -963,7 +1002,7 @@
         <v>38</v>
       </c>
       <c r="O19" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -980,7 +1019,7 @@
         <v>74</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>34</v>
@@ -1010,7 +1049,54 @@
         <v>38</v>
       </c>
       <c r="O20" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="K21" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="L21" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="M21" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="N21" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="O21" s="4" t="s">
+        <v>89</v>
       </c>
     </row>
   </sheetData>
